--- a/LISTAS_ORDENADAS/MI/Tenders Bnaqueta Barral/TENDEDERO CALESITA DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MI/Tenders Bnaqueta Barral/TENDEDERO CALESITA DISMAY.xlsx
@@ -770,14 +770,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45160.54497979794</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="25">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -827,16 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23" ht="22.5" customHeight="1" s="25"/>
     <row r="24" ht="22.5" customHeight="1" s="25"/>
     <row r="25" ht="22.5" customHeight="1" s="25"/>
@@ -929,10 +915,8 @@
         </is>
       </c>
       <c r="C37" s="23" t="n"/>
-      <c r="D37" s="20" t="inlineStr">
-        <is>
-          <t>***************</t>
-        </is>
+      <c r="D37" s="20" t="n">
+        <v>17717.317</v>
       </c>
     </row>
     <row r="38">
@@ -945,7 +929,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41" ht="18" customHeight="1" s="25">
       <c r="A41" s="28" t="n"/>
       <c r="B41" s="28" t="n"/>
@@ -965,35 +948,31 @@
     <row r="45" ht="19.5" customHeight="1" s="25">
       <c r="B45" s="24" t="n"/>
     </row>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48" ht="19.5" customHeight="1" s="25">
       <c r="A48" s="6" t="n"/>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="4" t="n"/>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
